--- a/Result/profitability/5222.xlsx
+++ b/Result/profitability/5222.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62125</v>
+        <v>0.48875</v>
       </c>
       <c r="N2" t="n">
-        <v>51.4625</v>
+        <v>50.46875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.55</v>
+        <v>0.4675</v>
       </c>
       <c r="N3" t="n">
-        <v>52.37875</v>
+        <v>51.89875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.335</v>
+        <v>0.2725</v>
       </c>
       <c r="N4" t="n">
-        <v>52.82125</v>
+        <v>52.0325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0.2675</v>
       </c>
       <c r="N5" t="n">
-        <v>51.81125</v>
+        <v>50.28875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -6653,6 +6653,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>229</v>
+      </c>
+      <c r="D50" t="n">
+        <v>121</v>
+      </c>
+      <c r="E50" t="n">
+        <v>107</v>
+      </c>
+      <c r="F50" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="G50" t="n">
+        <v>37</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>16.14%</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>42</v>
+      </c>
+      <c r="K50" t="n">
+        <v>36</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.72375</v>
+      </c>
+      <c r="N50" t="n">
+        <v>51.895</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.8636363636363635</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-7.079999999999998</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-0.1311839911061701</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>-0.2061960385982732</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
